--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2275,25 +2275,47 @@
       <c r="N32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="20" t="str">
+      <c r="A33" s="18" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="I33" s="20" t="n">
         <f aca="false">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J33" s="20" t="n">
         <f aca="false">IF(I33="","",1440-I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M33" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2319,25 +2319,47 @@
       <c r="N33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="20" t="str">
+      <c r="A34" s="18" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I34" s="20" t="n">
         <f aca="false">IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="20" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J34" s="20" t="n">
         <f aca="false">IF(I34="","",1440-I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
+        <v>30</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2363,25 +2363,47 @@
       <c r="N34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="20" t="str">
+      <c r="A35" s="18" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I35" s="20" t="n">
         <f aca="false">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J35" s="20" t="n">
         <f aca="false">IF(I35="","",1440-I35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K35" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2407,25 +2407,47 @@
       <c r="N35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="20" t="str">
+      <c r="A36" s="18" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I36" s="20" t="n">
         <f aca="false">IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="20" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J36" s="20" t="n">
         <f aca="false">IF(I36="","",1440-I36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M36" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2451,25 +2451,47 @@
       <c r="N36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="20" t="str">
+      <c r="A37" s="18" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I37" s="20" t="n">
         <f aca="false">IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J37" s="20" t="n">
         <f aca="false">IF(I37="","",1440-I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M37" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2495,25 +2495,47 @@
       <c r="N37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="20" t="str">
+      <c r="A38" s="18" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="I38" s="20" t="n">
         <f aca="false">IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J38" s="20" t="n">
         <f aca="false">IF(I38="","",1440-I38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="21"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2539,25 +2539,47 @@
       <c r="N38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20" t="str">
+      <c r="A39" s="18" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>720</v>
+      </c>
+      <c r="I39" s="20" t="n">
         <f aca="false">IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J39" s="20" t="n">
         <f aca="false">IF(I39="","",1440-I39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2583,25 +2583,47 @@
       <c r="N39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20" t="str">
+      <c r="A40" s="18" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="I40" s="20" t="n">
         <f aca="false">IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="20" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J40" s="20" t="n">
         <f aca="false">IF(I40="","",1440-I40)</f>
-        <v/>
-      </c>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
+        <v>30</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2627,25 +2627,47 @@
       <c r="N40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="20" t="str">
+      <c r="A41" s="18" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I41" s="20" t="n">
         <f aca="false">IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J41" s="20" t="n">
         <f aca="false">IF(I41="","",1440-I41)</f>
-        <v/>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M41" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2671,25 +2671,47 @@
       <c r="N41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="20" t="str">
+      <c r="A42" s="18" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>550</v>
+      </c>
+      <c r="I42" s="20" t="n">
         <f aca="false">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J42" s="20" t="n">
         <f aca="false">IF(I42="","",1440-I42)</f>
-        <v/>
-      </c>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M42" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2715,25 +2715,47 @@
       <c r="N42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="20" t="str">
+      <c r="A43" s="18" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I43" s="20" t="n">
         <f aca="false">IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J43" s="20" t="n">
         <f aca="false">IF(I43="","",1440-I43)</f>
-        <v/>
-      </c>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M43" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2759,25 +2759,47 @@
       <c r="N43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="20" t="str">
+      <c r="A44" s="18" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>630</v>
+      </c>
+      <c r="I44" s="20" t="n">
         <f aca="false">IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
-        <v/>
-      </c>
-      <c r="J44" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J44" s="20" t="n">
         <f aca="false">IF(I44="","",1440-I44)</f>
-        <v/>
-      </c>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M44" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2803,25 +2803,47 @@
       <c r="N44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="20" t="str">
+      <c r="A45" s="18" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B45" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C45" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>440</v>
+      </c>
+      <c r="I45" s="20" t="n">
         <f aca="false">IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
-        <v/>
-      </c>
-      <c r="J45" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J45" s="20" t="n">
         <f aca="false">IF(I45="","",1440-I45)</f>
-        <v/>
-      </c>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2847,25 +2847,47 @@
       <c r="N45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="20" t="str">
+      <c r="A46" s="18" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="I46" s="20" t="n">
         <f aca="false">IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
-        <v/>
-      </c>
-      <c r="J46" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J46" s="20" t="n">
         <f aca="false">IF(I46="","",1440-I46)</f>
-        <v/>
-      </c>
-      <c r="K46" s="21"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M46" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2891,25 +2891,47 @@
       <c r="N46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="20" t="str">
+      <c r="A47" s="18" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="I47" s="20" t="n">
         <f aca="false">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
-        <v/>
-      </c>
-      <c r="J47" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J47" s="20" t="n">
         <f aca="false">IF(I47="","",1440-I47)</f>
-        <v/>
-      </c>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K47" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2935,25 +2935,47 @@
       <c r="N47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="20" t="str">
+      <c r="A48" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="I48" s="20" t="n">
         <f aca="false">IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
-        <v/>
-      </c>
-      <c r="J48" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J48" s="20" t="n">
         <f aca="false">IF(I48="","",1440-I48)</f>
-        <v/>
-      </c>
-      <c r="K48" s="21"/>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M48" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2979,25 +2979,47 @@
       <c r="N48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="20" t="str">
+      <c r="A49" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C49" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="I49" s="20" t="n">
         <f aca="false">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
-        <v/>
-      </c>
-      <c r="J49" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J49" s="20" t="n">
         <f aca="false">IF(I49="","",1440-I49)</f>
-        <v/>
-      </c>
-      <c r="K49" s="21"/>
-      <c r="L49" s="21"/>
-      <c r="M49" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L49" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M49" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3023,25 +3023,47 @@
       <c r="N49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="20" t="str">
+      <c r="A50" s="18" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="I50" s="20" t="n">
         <f aca="false">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
-        <v/>
-      </c>
-      <c r="J50" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J50" s="20" t="n">
         <f aca="false">IF(I50="","",1440-I50)</f>
-        <v/>
-      </c>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3067,25 +3067,47 @@
       <c r="N50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="20" t="str">
+      <c r="A51" s="18" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="I51" s="20" t="n">
         <f aca="false">IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
-        <v/>
-      </c>
-      <c r="J51" s="20" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J51" s="20" t="n">
         <f aca="false">IF(I51="","",1440-I51)</f>
-        <v/>
-      </c>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
+        <v>30</v>
+      </c>
+      <c r="K51" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M51" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N51" s="22"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3111,25 +3111,47 @@
       <c r="N51" s="22"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="20" t="str">
+      <c r="A52" s="18" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="G52" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>530</v>
+      </c>
+      <c r="I52" s="20" t="n">
         <f aca="false">IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
-        <v/>
-      </c>
-      <c r="J52" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J52" s="20" t="n">
         <f aca="false">IF(I52="","",1440-I52)</f>
-        <v/>
-      </c>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M52" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3155,25 +3155,47 @@
       <c r="N52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="20" t="str">
+      <c r="A53" s="18" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B53" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="I53" s="20" t="n">
         <f aca="false">IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
-        <v/>
-      </c>
-      <c r="J53" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J53" s="20" t="n">
         <f aca="false">IF(I53="","",1440-I53)</f>
-        <v/>
-      </c>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
-      <c r="M53" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3199,25 +3199,47 @@
       <c r="N53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="20" t="str">
+      <c r="A54" s="18" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="I54" s="20" t="n">
         <f aca="false">IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
-        <v/>
-      </c>
-      <c r="J54" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J54" s="20" t="n">
         <f aca="false">IF(I54="","",1440-I54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L54" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N54" s="22"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3243,25 +3243,47 @@
       <c r="N54" s="22"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="20" t="str">
+      <c r="A55" s="18" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="19" t="n">
+        <v>930</v>
+      </c>
+      <c r="I55" s="20" t="n">
         <f aca="false">IF(SUM(B55:F55,H55)=0,"",SUM(B55:F55,H55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J55" s="20" t="n">
         <f aca="false">IF(I55="","",1440-I55)</f>
-        <v/>
-      </c>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M55" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3287,25 +3287,47 @@
       <c r="N55" s="22"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="18"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="20" t="str">
+      <c r="A56" s="18" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I56" s="20" t="n">
         <f aca="false">IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
-        <v/>
-      </c>
-      <c r="J56" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J56" s="20" t="n">
         <f aca="false">IF(I56="","",1440-I56)</f>
-        <v/>
-      </c>
-      <c r="K56" s="21"/>
-      <c r="L56" s="21"/>
-      <c r="M56" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K56" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M56" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N56" s="22"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3331,25 +3331,47 @@
       <c r="N56" s="22"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="20" t="str">
+      <c r="A57" s="18" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="I57" s="20" t="n">
         <f aca="false">IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
-        <v/>
-      </c>
-      <c r="J57" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J57" s="20" t="n">
         <f aca="false">IF(I57="","",1440-I57)</f>
-        <v/>
-      </c>
-      <c r="K57" s="21"/>
-      <c r="L57" s="21"/>
-      <c r="M57" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K57" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3375,25 +3375,47 @@
       <c r="N57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="20" t="str">
+      <c r="A58" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="I58" s="20" t="n">
         <f aca="false">IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
-        <v/>
-      </c>
-      <c r="J58" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J58" s="20" t="n">
         <f aca="false">IF(I58="","",1440-I58)</f>
-        <v/>
-      </c>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K58" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M58" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -3419,25 +3419,47 @@
       <c r="N58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="18"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="20" t="str">
+      <c r="A59" s="18" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B59" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>750</v>
+      </c>
+      <c r="I59" s="20" t="n">
         <f aca="false">IF(SUM(B59:F59,H59)=0,"",SUM(B59:F59,H59))</f>
-        <v/>
-      </c>
-      <c r="J59" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J59" s="20" t="n">
         <f aca="false">IF(I59="","",1440-I59)</f>
-        <v/>
-      </c>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L59" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N59" s="22"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
